--- a/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/www/ig/fhir/mesures/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T08:41:57+00:00</t>
+    <t>2026-02-18T13:49:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,7 +676,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -692,7 +692,8 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1353,7 +1354,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2488,17 +2489,17 @@
   <dimension ref="A1:AP117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.58984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.2265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2507,28 +2508,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="111.65625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="95.7265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4813,7 +4814,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -4909,7 +4910,7 @@
         <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>206</v>
+        <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>122</v>
@@ -5535,7 +5536,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>249</v>
       </c>
@@ -5775,7 +5776,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>272</v>
       </c>
@@ -6137,7 +6138,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>278</v>
       </c>
@@ -6497,7 +6498,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>291</v>
       </c>
@@ -6739,7 +6740,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>309</v>
       </c>
@@ -7223,7 +7224,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>345</v>
       </c>
@@ -8791,7 +8792,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>382</v>
       </c>
@@ -9155,7 +9156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>409</v>
       </c>
@@ -9637,7 +9638,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>450</v>
       </c>
@@ -9999,7 +10000,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>457</v>
       </c>
@@ -10243,7 +10244,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>478</v>
       </c>
@@ -10363,7 +10364,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>486</v>
       </c>
@@ -10483,7 +10484,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>495</v>
       </c>
@@ -10605,7 +10606,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>504</v>
       </c>
@@ -13735,7 +13736,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>563</v>
       </c>
@@ -13975,7 +13976,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>580</v>
       </c>
@@ -15535,7 +15536,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>655</v>
       </c>
@@ -16017,7 +16018,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>665</v>
       </c>
@@ -16139,7 +16140,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>671</v>
       </c>
@@ -16204,7 +16205,7 @@
         <v>82</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="Y114" t="s" s="2">
         <v>676</v>
@@ -16261,7 +16262,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>680</v>
       </c>
@@ -16629,12 +16630,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP117">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
